--- a/Materiales_Horometro.xlsx
+++ b/Materiales_Horometro.xlsx
@@ -1,14 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planta\Documents\Horometro\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31323E5C-D4C6-470B-9B91-A2671EAF90CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$1</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -18,15 +28,309 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Costo Unitario</t>
+  </si>
+  <si>
+    <t>Costo Final</t>
+  </si>
+  <si>
+    <t>Proveedor</t>
+  </si>
+  <si>
+    <t>Dirección</t>
+  </si>
+  <si>
+    <t>Pantalla LCD 0x27</t>
+  </si>
+  <si>
+    <t>Botoneras</t>
+  </si>
+  <si>
+    <t>Raspberry Pi Zero</t>
+  </si>
+  <si>
+    <t>Micro SD</t>
+  </si>
+  <si>
+    <t>Pin Físico (Header)</t>
+  </si>
+  <si>
+    <t>Pin BCM (Código)</t>
+  </si>
+  <si>
+    <t>Función</t>
+  </si>
+  <si>
+    <t>LCD VCC</t>
+  </si>
+  <si>
+    <t>5V</t>
+  </si>
+  <si>
+    <t>Alimentación Pantalla</t>
+  </si>
+  <si>
+    <t>LCD GND</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>Tierra Común</t>
+  </si>
+  <si>
+    <t>LCD SDA</t>
+  </si>
+  <si>
+    <t>GPIO 2 (SDA)</t>
+  </si>
+  <si>
+    <t>Datos I2C</t>
+  </si>
+  <si>
+    <t>LCD SCL</t>
+  </si>
+  <si>
+    <t>GPIO 3 (SCL)</t>
+  </si>
+  <si>
+    <t>Reloj I2C</t>
+  </si>
+  <si>
+    <t>Botón UP</t>
+  </si>
+  <si>
+    <t>GPIO 27</t>
+  </si>
+  <si>
+    <t>Navegar Menú</t>
+  </si>
+  <si>
+    <t>Botón DOWN</t>
+  </si>
+  <si>
+    <t>GPIO 22</t>
+  </si>
+  <si>
+    <t>Botón OK</t>
+  </si>
+  <si>
+    <t>GPIO 23</t>
+  </si>
+  <si>
+    <t>Confirmar Selección</t>
+  </si>
+  <si>
+    <t>Señal VFD</t>
+  </si>
+  <si>
+    <t>GPIO 17</t>
+  </si>
+  <si>
+    <t>Entrada Sensor Motor (Aislada)</t>
+  </si>
+  <si>
+    <t>Origen (Variador iS7)</t>
+  </si>
+  <si>
+    <t>Destino (Optoacoplador PC817)</t>
+  </si>
+  <si>
+    <t>Componente Adicional / Notas</t>
+  </si>
+  <si>
+    <r>
+      <t>Terminal 24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Fuente 24V)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Pin 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Ánodo)</t>
+    </r>
+  </si>
+  <si>
+    <t>Conexión directa.</t>
+  </si>
+  <si>
+    <r>
+      <t>Terminal Q1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Salida Digital)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Pin 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Cátodo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Insertar Resistencia de 2.2kΩ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en serie entre Q1 y el Pin 2.</t>
+    </r>
+  </si>
+  <si>
+    <t>GND (Raspberry Pi)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pin 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Emisor)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tierra común de la lógica de la Raspberry.</t>
+  </si>
+  <si>
+    <t>GPIO 17 (Raspberry Pi)</t>
+  </si>
+  <si>
+    <r>
+      <t>Pin 4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Colector)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Configurar este pin como </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF444746"/>
+        <rFont val="Google Sans Text"/>
+        <family val="2"/>
+      </rPr>
+      <t>INPUT_PULLUP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> en el código.</t>
+    </r>
+  </si>
+  <si>
+    <t>Optoacoplador PC817</t>
+  </si>
+  <si>
+    <t>PLC-OSC- 24DC/ 24DC/ 2</t>
+  </si>
+  <si>
+    <t>Finder Serie 38.51</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF444746"/>
+      <name val="Google Sans Text"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +341,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +349,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +662,280 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD3FB0F7-37CB-43D1-80C5-A4BA51C53663}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="60.75" thickBot="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="59.25" thickBot="1">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="103.5" thickBot="1">
+      <c r="A3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="72" thickBot="1">
+      <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="84.75" thickBot="1">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30.75" thickBot="1">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3">
+        <v>13</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30.75" thickBot="1">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="30.75" thickBot="1">
+      <c r="A8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="57.75" thickBot="1">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Materiales_Horometro.xlsx
+++ b/Materiales_Horometro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planta\Documents\Horometro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31323E5C-D4C6-470B-9B91-A2671EAF90CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885EF32F-F8EB-4FC6-B4BE-F686302A0C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,17 +19,28 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>Componente</t>
   </si>
@@ -50,12 +61,6 @@
   </si>
   <si>
     <t>Dirección</t>
-  </si>
-  <si>
-    <t>Pantalla LCD 0x27</t>
-  </si>
-  <si>
-    <t>Botoneras</t>
   </si>
   <si>
     <t>Raspberry Pi Zero</t>
@@ -284,20 +289,45 @@
     </r>
   </si>
   <si>
-    <t>Optoacoplador PC817</t>
-  </si>
-  <si>
-    <t>PLC-OSC- 24DC/ 24DC/ 2</t>
-  </si>
-  <si>
-    <t>Finder Serie 38.51</t>
+    <t>Pantalla LCD 20x4</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Resistencias 2.2kOhm</t>
+  </si>
+  <si>
+    <t>SRD-05VDC-SL-C</t>
+  </si>
+  <si>
+    <t>Módulo SSR</t>
+  </si>
+  <si>
+    <t>Modulo Optoacoplador PC817</t>
+  </si>
+  <si>
+    <t>Pulsador NEMA 22mm</t>
+  </si>
+  <si>
+    <t>Rojo, Verde y 2 Negros</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;\ * #,##0.00_);_(&quot;$&quot;\ * \(#,##0.00\);_(&quot;$&quot;\ * &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="6">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,26 +395,30 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -663,11 +697,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="28.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
@@ -698,58 +732,134 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
+      <c r="D2" s="7">
+        <v>40</v>
+      </c>
+      <c r="E2" s="6">
+        <f>D2*C2</f>
+        <v>40</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
+      <c r="D3" s="7">
+        <v>15</v>
+      </c>
+      <c r="E3" s="6">
+        <f t="shared" ref="E3:E9" si="0">D3*C3</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
+      <c r="D4" s="7">
+        <v>12.8</v>
+      </c>
+      <c r="E4" s="6">
+        <f t="shared" si="0"/>
+        <v>12.8</v>
+      </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
+        <v>57</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
+      <c r="D5" s="7">
+        <v>0.27</v>
+      </c>
+      <c r="E5" s="6">
+        <f t="shared" si="0"/>
+        <v>1.08</v>
+      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
+      <c r="D6" s="7">
+        <v>5</v>
+      </c>
+      <c r="E6" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
+      <c r="D7" s="7">
+        <v>5</v>
+      </c>
+      <c r="E7" s="6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>1</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <f>D8*C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="E9" s="6">
+        <f>D9*C9</f>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="D10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" s="6">
+        <f>SUM(E2:E9)</f>
+        <v>79.28</v>
       </c>
     </row>
   </sheetData>
@@ -768,170 +878,170 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="59.25" thickBot="1">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="103.5" thickBot="1">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72" thickBot="1">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="84.75" thickBot="1">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30.75" thickBot="1">
       <c r="A6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30.75" thickBot="1">
       <c r="A7" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30.75" thickBot="1">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="57.75" thickBot="1">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Materiales_Horometro.xlsx
+++ b/Materiales_Horometro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planta\Documents\Horometro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885EF32F-F8EB-4FC6-B4BE-F686302A0C95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66656C9-D80F-4D4E-80AD-884D546A31BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3915" yWindow="0" windowWidth="11520" windowHeight="10710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
   <si>
     <t>Componente</t>
   </si>
@@ -61,9 +61,6 @@
   </si>
   <si>
     <t>Dirección</t>
-  </si>
-  <si>
-    <t>Raspberry Pi Zero</t>
   </si>
   <si>
     <t>Micro SD</t>
@@ -298,12 +295,6 @@
     <t>Resistencias 2.2kOhm</t>
   </si>
   <si>
-    <t>SRD-05VDC-SL-C</t>
-  </si>
-  <si>
-    <t>Módulo SSR</t>
-  </si>
-  <si>
     <t>Modulo Optoacoplador PC817</t>
   </si>
   <si>
@@ -311,6 +302,87 @@
   </si>
   <si>
     <t>Rojo, Verde y 2 Negros</t>
+  </si>
+  <si>
+    <t>Convertidor Buck DC-DC</t>
+  </si>
+  <si>
+    <t>Raspberry Pi Zero 2W</t>
+  </si>
+  <si>
+    <t>Entrada 24V, salida 3.3 V</t>
+  </si>
+  <si>
+    <t>Tapia</t>
+  </si>
+  <si>
+    <t>32 GB</t>
+  </si>
+  <si>
+    <t>1/2 W</t>
+  </si>
+  <si>
+    <t>Cable Multifilar</t>
+  </si>
+  <si>
+    <t>Cable Apantallado</t>
+  </si>
+  <si>
+    <t>Cable 5V</t>
+  </si>
+  <si>
+    <t>24 AWG (com interna, GPIO)</t>
+  </si>
+  <si>
+    <t>22 AWG 4/5 hilos (botones)</t>
+  </si>
+  <si>
+    <t>18 AWG (alimentación)</t>
+  </si>
+  <si>
+    <t>Orellana</t>
+  </si>
+  <si>
+    <t>Opto bornera</t>
+  </si>
+  <si>
+    <t>100358721, pag 4/20</t>
+  </si>
+  <si>
+    <t>State Relay SSR-25DD</t>
+  </si>
+  <si>
+    <t>Input 3-32VDC To Output 5-240VDC 25A Single Phase Plastic Cover</t>
+  </si>
+  <si>
+    <t>Convertidor DC-DC</t>
+  </si>
+  <si>
+    <t>12V 24V a 5V 3A 15W Micro USB C Buck Convertidor</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>JNEG</t>
+  </si>
+  <si>
+    <t>&lt;121872A&gt;4 PARES, 23 AWG, 300V</t>
+  </si>
+  <si>
+    <t>CABLE DE COMUNICACION
+ETHERNET CAT6 UTP</t>
+  </si>
+  <si>
+    <t>CABLE RS-485 COBRE
+ESTAÑADO</t>
+  </si>
+  <si>
+    <t>&lt;3105A&gt; 2X22 AWG PAR
+TRENZADO BLINDADO</t>
+  </si>
+  <si>
+    <t>Cablecom</t>
   </si>
 </sst>
 </file>
@@ -363,12 +435,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -399,7 +477,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -415,7 +493,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -697,11 +784,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
@@ -732,138 +819,246 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="7">
-        <v>40</v>
+      <c r="D2" s="6">
+        <v>49.5</v>
       </c>
       <c r="E2" s="6">
         <f>D2*C2</f>
-        <v>40</v>
+        <v>49.5</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>59</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
-      <c r="D3" s="7">
-        <v>15</v>
+      <c r="D3" s="6">
+        <v>12.5</v>
       </c>
       <c r="E3" s="6">
-        <f t="shared" ref="E3:E9" si="0">D3*C3</f>
-        <v>15</v>
-      </c>
+        <f t="shared" ref="E3" si="0">D3*C3</f>
+        <v>12.5</v>
+      </c>
+      <c r="F3" s="7"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
-      <c r="D4" s="7">
-        <v>12.8</v>
+      <c r="D4" s="6">
+        <v>6.96</v>
       </c>
       <c r="E4" s="6">
-        <f t="shared" si="0"/>
-        <v>12.8</v>
+        <f>D4*C4*1.12</f>
+        <v>7.7952000000000004</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.27</v>
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>0.04</v>
       </c>
       <c r="E5" s="6">
-        <f t="shared" si="0"/>
-        <v>1.08</v>
-      </c>
+        <f t="shared" ref="E5:E7" si="1">D5*C5*1.12</f>
+        <v>0.44800000000000006</v>
+      </c>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="7">
-        <v>5</v>
+      <c r="D6" s="6">
+        <v>0.85</v>
       </c>
       <c r="E6" s="6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>0.95200000000000007</v>
+      </c>
+      <c r="F6" s="7"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" s="7">
-        <v>5</v>
+      <c r="D7" s="6">
+        <v>1.65</v>
       </c>
       <c r="E7" s="6">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
+        <f t="shared" si="1"/>
+        <v>1.8480000000000001</v>
+      </c>
+      <c r="F7" s="7"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>70</v>
+      </c>
+      <c r="B8" t="s">
+        <v>71</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="7">
-        <v>0</v>
+      <c r="D8" s="6">
+        <v>43.02</v>
       </c>
       <c r="E8" s="6">
         <f>D8*C8</f>
-        <v>0</v>
+        <v>43.02</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>72</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
       </c>
       <c r="C9">
-        <v>10</v>
-      </c>
-      <c r="D9" s="7">
-        <v>0.04</v>
+        <v>1</v>
+      </c>
+      <c r="D9" s="6">
+        <v>43.91</v>
       </c>
       <c r="E9" s="6">
         <f>D9*C9</f>
-        <v>0.4</v>
-      </c>
+        <v>43.91</v>
+      </c>
+      <c r="F9" s="7"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="D10" s="5" t="s">
-        <v>51</v>
+      <c r="A10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10" s="6">
+        <v>9.1199999999999992</v>
       </c>
       <c r="E10" s="6">
-        <f>SUM(E2:E9)</f>
-        <v>79.28</v>
+        <f>D10*C10</f>
+        <v>36.479999999999997</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="30">
+      <c r="A11" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30">
+      <c r="A12" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="D13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="6">
+        <f>SUM(E2:E12)</f>
+        <v>196.45319999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14">
+        <v>52.18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <mergeCells count="4">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F11:F12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -878,170 +1073,170 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="59.25" thickBot="1">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3">
         <v>2</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>14</v>
-      </c>
       <c r="F2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="103.5" thickBot="1">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3">
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="72" thickBot="1">
       <c r="A4" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3">
         <v>3</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="84.75" thickBot="1">
       <c r="A5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" s="3">
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>23</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30.75" thickBot="1">
       <c r="A6" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30.75" thickBot="1">
       <c r="A7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3">
         <v>15</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30.75" thickBot="1">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="57.75" thickBot="1">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
         <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/Materiales_Horometro.xlsx
+++ b/Materiales_Horometro.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planta\Documents\Horometro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66656C9-D80F-4D4E-80AD-884D546A31BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4496BADD-8669-4A1D-BC94-5A241CA5F889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3915" yWindow="0" windowWidth="11520" windowHeight="10710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="83">
   <si>
     <t>Componente</t>
   </si>
@@ -304,18 +304,12 @@
     <t>Rojo, Verde y 2 Negros</t>
   </si>
   <si>
-    <t>Convertidor Buck DC-DC</t>
-  </si>
-  <si>
     <t>Raspberry Pi Zero 2W</t>
   </si>
   <si>
     <t>Entrada 24V, salida 3.3 V</t>
   </si>
   <si>
-    <t>Tapia</t>
-  </si>
-  <si>
     <t>32 GB</t>
   </si>
   <si>
@@ -340,15 +334,6 @@
     <t>18 AWG (alimentación)</t>
   </si>
   <si>
-    <t>Orellana</t>
-  </si>
-  <si>
-    <t>Opto bornera</t>
-  </si>
-  <si>
-    <t>100358721, pag 4/20</t>
-  </si>
-  <si>
     <t>State Relay SSR-25DD</t>
   </si>
   <si>
@@ -362,9 +347,6 @@
   </si>
   <si>
     <t>Amazon</t>
-  </si>
-  <si>
-    <t>JNEG</t>
   </si>
   <si>
     <t>&lt;121872A&gt;4 PARES, 23 AWG, 300V</t>
@@ -383,6 +365,30 @@
   </si>
   <si>
     <t>Cablecom</t>
+  </si>
+  <si>
+    <t>Tapia Electronics</t>
+  </si>
+  <si>
+    <t>Electrónica Orellana</t>
+  </si>
+  <si>
+    <t>Boyacá y Francisco Illingworth Icaza 1011 y, 090306 Guayaquil</t>
+  </si>
+  <si>
+    <t>P.icaza y Boyacá 706 y, 090312 Guayaquil</t>
+  </si>
+  <si>
+    <t>https://a.co/d/02bu7pRZ</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0i9TpS0D</t>
+  </si>
+  <si>
+    <t>Siemens</t>
+  </si>
+  <si>
+    <t>Con I2C</t>
   </si>
 </sst>
 </file>
@@ -392,7 +398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;\ * #,##0.00_);_(&quot;$&quot;\ * \(#,##0.00\);_(&quot;$&quot;\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +440,14 @@
       <name val="Google Sans Text"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -473,11 +487,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -493,9 +508,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -503,8 +515,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -784,14 +807,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
     <col min="2" max="2" width="26.42578125" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -817,9 +841,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" ht="15" customHeight="1">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -831,8 +855,11 @@
         <f>D2*C2</f>
         <v>49.5</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>58</v>
+      <c r="F2" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -840,7 +867,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -852,12 +879,16 @@
         <f t="shared" ref="E3" si="0">D3*C3</f>
         <v>12.5</v>
       </c>
-      <c r="F3" s="7"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>49</v>
       </c>
+      <c r="B4" t="s">
+        <v>82</v>
+      </c>
       <c r="C4">
         <v>1</v>
       </c>
@@ -868,8 +899,11 @@
         <f>D4*C4*1.12</f>
         <v>7.7952000000000004</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>67</v>
+      <c r="F4" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -877,7 +911,7 @@
         <v>51</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C5">
         <v>10</v>
@@ -886,17 +920,18 @@
         <v>0.04</v>
       </c>
       <c r="E5" s="6">
-        <f t="shared" ref="E5:E7" si="1">D5*C5*1.12</f>
+        <f t="shared" ref="E5:E6" si="1">D5*C5*1.12</f>
         <v>0.44800000000000006</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -908,157 +943,143 @@
         <f t="shared" si="1"/>
         <v>0.95200000000000007</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="12"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7" s="6">
-        <v>1.65</v>
+        <v>43.02</v>
       </c>
       <c r="E7" s="6">
-        <f t="shared" si="1"/>
-        <v>1.8480000000000001</v>
-      </c>
-      <c r="F7" s="7"/>
+        <f>D7*C7</f>
+        <v>43.02</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" s="6">
-        <v>43.02</v>
+        <v>43.91</v>
       </c>
       <c r="E8" s="6">
         <f>D8*C8</f>
-        <v>43.02</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>74</v>
+        <v>43.91</v>
+      </c>
+      <c r="F8" s="10"/>
+      <c r="G8" s="13" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D9" s="6">
-        <v>43.91</v>
+        <v>9.1199999999999992</v>
       </c>
       <c r="E9" s="6">
         <f>D9*C9</f>
-        <v>43.91</v>
-      </c>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10" s="6">
-        <v>9.1199999999999992</v>
-      </c>
-      <c r="E10" s="6">
-        <f>D10*C10</f>
         <v>36.479999999999997</v>
       </c>
+      <c r="F9" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="30">
+      <c r="A10" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>73</v>
+      </c>
       <c r="F10" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30">
-      <c r="A11" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30">
-      <c r="A12" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="D13" s="5" t="s">
+      <c r="A11" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="D12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="6">
-        <f>SUM(E2:E12)</f>
-        <v>196.45319999999998</v>
+      <c r="E12" s="6">
+        <f>SUM(E2:E11)</f>
+        <v>194.60519999999997</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14">
-        <v>52.18</v>
+      <c r="A14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="G4:G6"/>
     <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F7"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{3D913592-3BBF-49E5-A6A5-E13446141306}"/>
+    <hyperlink ref="G7" r:id="rId2" xr:uid="{A337CD22-5308-43FD-8AEE-339494E5C4AC}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
